--- a/teste_resultado.xlsx
+++ b/teste_resultado.xlsx
@@ -440,7 +440,7 @@
         <v>Portaria DIGER/CENSIPAM/SG-MD nº 4783, de 26 de setembro de 2023</v>
       </c>
       <c r="D4" t="str">
-        <v>Nenhum resultado encontrado</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="5">
